--- a/test/vedomost_05_2026.xlsx
+++ b/test/vedomost_05_2026.xlsx
@@ -1115,22 +1115,22 @@
         <v>836.5599999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>733.83</v>
+        <v>836.5599999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>101.12</v>
+        <v>115.28</v>
       </c>
       <c r="W11" t="n">
-        <v>735.4400000000001</v>
+        <v>618.55</v>
       </c>
       <c r="X11" t="n">
-        <v>73.54000000000001</v>
+        <v>61.86</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>661.9</v>
+        <v>659.42</v>
       </c>
     </row>
     <row r="12">
@@ -1505,22 +1505,22 @@
         <v>10582.31</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>10479.58</v>
+        <v>10582.31</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1444.08</v>
+        <v>1458.24</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>9138.23</v>
+        <v>9021.34</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>913.83</v>
+        <v>902.15</v>
       </c>
       <c r="Y16" s="4" t="n">
         <v>500</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>7734.7</v>
+        <v>7732.22</v>
       </c>
     </row>
     <row r="18">

--- a/test/vedomost_05_2026.xlsx
+++ b/test/vedomost_05_2026.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1478,53 +1478,139 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="4" t="inlineStr">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Росица Кънчева</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Оператор склад</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2019-10-01</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>18</v>
+      </c>
+      <c r="H16" t="n">
+        <v>160</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>16</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>900</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1128.58</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1128.58</v>
+      </c>
+      <c r="V16" t="n">
+        <v>155.52</v>
+      </c>
+      <c r="W16" t="n">
+        <v>973.0599999999999</v>
+      </c>
+      <c r="X16" t="n">
+        <v>97.31</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>875.75</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>ОБЩО</t>
         </is>
       </c>
-      <c r="M16" s="4" t="n">
-        <v>9933.93</v>
-      </c>
-      <c r="O16" s="4" t="n">
-        <v>446.76</v>
-      </c>
-      <c r="P16" s="4" t="n">
-        <v>55.56</v>
-      </c>
-      <c r="Q16" s="4" t="n">
-        <v>43.33</v>
-      </c>
-      <c r="R16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="4" t="n">
+      <c r="M17" s="4" t="n">
+        <v>10833.93</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>479.16</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>133.26</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>146.93</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="S17" s="4" t="n">
         <v>102.73</v>
       </c>
-      <c r="T16" s="4" t="n">
-        <v>10582.31</v>
-      </c>
-      <c r="U16" s="4" t="n">
-        <v>10582.31</v>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>1458.24</v>
-      </c>
-      <c r="W16" s="4" t="n">
-        <v>9021.34</v>
-      </c>
-      <c r="X16" s="4" t="n">
-        <v>902.15</v>
-      </c>
-      <c r="Y16" s="4" t="n">
+      <c r="T17" s="4" t="n">
+        <v>11710.89</v>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>11710.89</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>1613.76</v>
+      </c>
+      <c r="W17" s="4" t="n">
+        <v>9994.4</v>
+      </c>
+      <c r="X17" s="4" t="n">
+        <v>999.46</v>
+      </c>
+      <c r="Y17" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="Z16" s="4" t="n">
-        <v>7732.22</v>
+      <c r="Z17" s="4" t="n">
+        <v>8607.969999999999</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Валута: EUR. Изготвил: ТРЗ отдел. Дата: 05.06.2026 г.</t>
         </is>
